--- a/ES_NQ_UPDATED___15min____FIXED.xlsx
+++ b/ES_NQ_UPDATED___15min____FIXED.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Z_0_5_Trades" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Z_0_5_Charts" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Z_1_Trades" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Z_1_Charts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Z_1_5_Trades" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Z_1_5_Charts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Z_2_Trades" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Z_2_Charts" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Z_2_5_Trades" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Z_2_5_Charts" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Z_3_Trades" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Z_3_Charts" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Summary" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Z_Performance_Matrix" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_0_5_Trades" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_0_5_Charts" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_1_Trades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_1_Charts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_1_5_Trades" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_1_5_Charts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_2_Trades" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_2_Charts" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_2_5_Trades" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_2_5_Charts" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_3_Trades" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_3_Charts" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Z_Performance_Matrix" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -138,7 +138,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -153,13 +153,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -168,7 +168,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -183,13 +183,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -213,13 +213,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -228,7 +228,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -243,13 +243,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -258,7 +258,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -273,13 +273,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -288,7 +288,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -303,13 +303,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom prst="rect"/>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
